--- a/缓存数据/newOdercityCsm.xlsx
+++ b/缓存数据/newOdercityCsm.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93.08</v>
+        <v>78.28</v>
       </c>
       <c r="C2" t="n">
-        <v>601.59</v>
+        <v>488.05</v>
       </c>
       <c r="D2" t="n">
-        <v>11.67</v>
+        <v>4.34</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.28</v>
+        <v>137.4</v>
       </c>
       <c r="C3" t="n">
-        <v>488.05</v>
+        <v>633.9</v>
       </c>
       <c r="D3" t="n">
-        <v>4.34</v>
+        <v>6.97</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -495,13 +495,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>137.4</v>
+        <v>116.42</v>
       </c>
       <c r="C4" t="n">
-        <v>633.9</v>
+        <v>445.58</v>
       </c>
       <c r="D4" t="n">
-        <v>6.97</v>
+        <v>1.32</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -514,13 +514,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>116.42</v>
+        <v>69.88</v>
       </c>
       <c r="C5" t="n">
-        <v>445.58</v>
+        <v>387.11</v>
       </c>
       <c r="D5" t="n">
-        <v>1.32</v>
+        <v>5.91</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69.88</v>
+        <v>129.53</v>
       </c>
       <c r="C6" t="n">
-        <v>387.11</v>
+        <v>421.46</v>
       </c>
       <c r="D6" t="n">
-        <v>5.91</v>
+        <v>8.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129.53</v>
+        <v>70.5</v>
       </c>
       <c r="C7" t="n">
-        <v>421.46</v>
+        <v>405.55</v>
       </c>
       <c r="D7" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -571,13 +571,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70.5</v>
+        <v>113.18</v>
       </c>
       <c r="C8" t="n">
-        <v>405.55</v>
+        <v>429.71</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>16.92</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113.18</v>
+        <v>124.65</v>
       </c>
       <c r="C9" t="n">
-        <v>429.71</v>
+        <v>383.1</v>
       </c>
       <c r="D9" t="n">
-        <v>16.92</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>

--- a/缓存数据/newOdercityCsm.xlsx
+++ b/缓存数据/newOdercityCsm.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78.28</v>
+        <v>3698.77</v>
       </c>
       <c r="C2" t="n">
-        <v>488.05</v>
+        <v>30947.3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.34</v>
+        <v>793.35</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>137.4</v>
+        <v>6555.249999999998</v>
       </c>
       <c r="C3" t="n">
-        <v>633.9</v>
+        <v>27076.59</v>
       </c>
       <c r="D3" t="n">
-        <v>6.97</v>
+        <v>4431.469999999999</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -495,13 +495,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116.42</v>
+        <v>4827.250000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>445.58</v>
+        <v>27369.19</v>
       </c>
       <c r="D4" t="n">
-        <v>1.32</v>
+        <v>1924.64</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -514,13 +514,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69.88</v>
+        <v>2293.05</v>
       </c>
       <c r="C5" t="n">
-        <v>387.11</v>
+        <v>32024.86</v>
       </c>
       <c r="D5" t="n">
-        <v>5.91</v>
+        <v>664.3599999999999</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>129.53</v>
+        <v>2367.19</v>
       </c>
       <c r="C6" t="n">
-        <v>421.46</v>
+        <v>31331.11</v>
       </c>
       <c r="D6" t="n">
-        <v>8.75</v>
+        <v>143.71</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70.5</v>
+        <v>2018.24</v>
       </c>
       <c r="C7" t="n">
-        <v>405.55</v>
+        <v>25644.13</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>327.04</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -571,13 +571,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>113.18</v>
+        <v>2515.579999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>429.71</v>
+        <v>29318.65</v>
       </c>
       <c r="D8" t="n">
-        <v>16.92</v>
+        <v>759.53</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -590,19 +590,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124.65</v>
+        <v>2331.34</v>
       </c>
       <c r="C9" t="n">
-        <v>383.1</v>
+        <v>30568.56</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>184.73</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>